--- a/data/sample/remal/Forecasted_Impact_1dlt.xlsx
+++ b/data/sample/remal/Forecasted_Impact_1dlt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim\IBF-Analysis\data\sample\remal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9593A7C6-4141-4804-A77A-CDBC429B5016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3698F611-FCC6-45F0-875E-31FFE62D74AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3994,7 +3994,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AL547"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4136,7 +4135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>100409</v>
       </c>
@@ -4219,7 +4218,7 @@
         <v>0.55413907514134353</v>
       </c>
       <c r="X2" s="2" t="str">
-        <f t="shared" ref="X2:X43" si="12">IF(W2&gt;0.7,"High",IF(W2&gt;0.3,"Moderate",IF(W2&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="X2:X65" si="12">IF(W2&gt;0.7,"High",IF(W2&gt;0.3,"Moderate",IF(W2&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
       <c r="Y2" s="2">
@@ -4255,11 +4254,11 @@
         <v>0.6107378529121692</v>
       </c>
       <c r="AG2" s="2" t="str">
-        <f t="shared" ref="AG2:AG39" si="21">IF(AF2&gt;0.7,"High",IF(AF2&gt;0.3,"Moderate",IF(AF2&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="AG2:AG65" si="21">IF(AF2&gt;0.7,"High",IF(AF2&gt;0.3,"Moderate",IF(AF2&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
     </row>
-    <row r="3" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>100419</v>
       </c>
@@ -4381,7 +4380,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="4" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>100428</v>
       </c>
@@ -4513,7 +4512,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="5" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>100447</v>
       </c>
@@ -4650,7 +4649,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="6" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>100485</v>
       </c>
@@ -4788,7 +4787,7 @@
         <v>123.8624964</v>
       </c>
     </row>
-    <row r="7" spans="1:37" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>100490</v>
       </c>
@@ -4926,7 +4925,7 @@
         <v>65.899999999999991</v>
       </c>
     </row>
-    <row r="8" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>100602</v>
       </c>
@@ -5062,7 +5061,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="9" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>100603</v>
       </c>
@@ -5198,7 +5197,7 @@
         <v>211353</v>
       </c>
     </row>
-    <row r="10" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>100607</v>
       </c>
@@ -5334,7 +5333,7 @@
         <v>0.6394367442212413</v>
       </c>
     </row>
-    <row r="11" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>100610</v>
       </c>
@@ -5471,7 +5470,7 @@
         <v>0.86565836200000001</v>
       </c>
     </row>
-    <row r="12" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>100632</v>
       </c>
@@ -5607,7 +5606,7 @@
         <v>0.34539999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>100636</v>
       </c>
@@ -5743,7 +5742,7 @@
         <v>0.68336417439816732</v>
       </c>
     </row>
-    <row r="14" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>100651</v>
       </c>
@@ -5880,7 +5879,7 @@
         <v>0.5955093140443154</v>
       </c>
     </row>
-    <row r="15" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>100662</v>
       </c>
@@ -6016,7 +6015,7 @@
         <v>0.46256248364947139</v>
       </c>
     </row>
-    <row r="16" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>100669</v>
       </c>
@@ -6152,7 +6151,7 @@
         <v>0.14676755835169378</v>
       </c>
     </row>
-    <row r="17" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>100694</v>
       </c>
@@ -6273,7 +6272,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="18" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>100918</v>
       </c>
@@ -6396,7 +6395,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="19" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>100921</v>
       </c>
@@ -6518,7 +6517,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="20" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>100925</v>
       </c>
@@ -6640,7 +6639,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="21" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>100929</v>
       </c>
@@ -6762,7 +6761,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="22" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>100954</v>
       </c>
@@ -6884,7 +6883,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="23" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>100965</v>
       </c>
@@ -7005,7 +7004,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="24" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>100991</v>
       </c>
@@ -7126,7 +7125,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="25" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>104240</v>
       </c>
@@ -7247,7 +7246,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="26" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>104243</v>
       </c>
@@ -7368,7 +7367,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="27" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>104273</v>
       </c>
@@ -7489,7 +7488,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="28" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>104284</v>
       </c>
@@ -7610,7 +7609,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="29" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>107838</v>
       </c>
@@ -7733,7 +7732,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="30" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>107852</v>
       </c>
@@ -7855,7 +7854,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="31" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>107855</v>
       </c>
@@ -7977,7 +7976,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="32" spans="1:33" s="18" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18">
         <v>107857</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="33" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>107866</v>
       </c>
@@ -8223,7 +8222,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="34" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>107876</v>
       </c>
@@ -8345,7 +8344,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="35" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>107895</v>
       </c>
@@ -8468,7 +8467,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="36" spans="1:38" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>107897</v>
       </c>
@@ -8592,7 +8591,7 @@
       </c>
       <c r="AL36" s="2"/>
     </row>
-    <row r="37" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>107914</v>
       </c>
@@ -8715,7 +8714,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="38" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>107947</v>
       </c>
@@ -8837,7 +8836,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="39" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>107958</v>
       </c>
@@ -8960,7 +8959,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="40" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>107976</v>
       </c>
@@ -9082,7 +9081,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="41" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>107980</v>
       </c>
@@ -9204,7 +9203,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="42" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>107987</v>
       </c>
@@ -9326,7 +9325,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="43" spans="1:38" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>107990</v>
       </c>
@@ -9449,7 +9448,7 @@
       </c>
       <c r="AL43" s="2"/>
     </row>
-    <row r="44" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>200304</v>
       </c>
@@ -9570,7 +9569,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="45" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>200314</v>
       </c>
@@ -9691,7 +9690,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="46" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>200351</v>
       </c>
@@ -9812,7 +9811,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="47" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>200373</v>
       </c>
@@ -9933,7 +9932,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="48" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>200389</v>
       </c>
@@ -10054,7 +10053,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="49" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>200391</v>
       </c>
@@ -10175,7 +10174,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="50" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>200395</v>
       </c>
@@ -10296,7 +10295,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="51" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>201202</v>
       </c>
@@ -10417,7 +10416,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="52" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>201204</v>
       </c>
@@ -10538,7 +10537,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="53" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>201207</v>
       </c>
@@ -10659,7 +10658,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="54" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>201213</v>
       </c>
@@ -10780,7 +10779,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="55" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>201233</v>
       </c>
@@ -10901,7 +10900,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="56" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>201263</v>
       </c>
@@ -11022,7 +11021,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="57" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>201285</v>
       </c>
@@ -11143,7 +11142,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="58" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>201290</v>
       </c>
@@ -11264,7 +11263,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="59" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>201294</v>
       </c>
@@ -11385,7 +11384,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="60" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>201322</v>
       </c>
@@ -11506,7 +11505,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="61" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>201345</v>
       </c>
@@ -11627,7 +11626,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="62" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>201347</v>
       </c>
@@ -11748,7 +11747,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="63" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>201349</v>
       </c>
@@ -11869,7 +11868,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="64" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>201358</v>
       </c>
@@ -11990,7 +11989,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="65" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>201376</v>
       </c>
@@ -12111,7 +12110,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="66" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>201379</v>
       </c>
@@ -12232,7 +12231,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="67" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>201395</v>
       </c>
@@ -15499,7 +15498,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="94" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>201909</v>
       </c>
@@ -15620,7 +15619,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="95" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>201915</v>
       </c>
@@ -15741,7 +15740,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="96" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>201918</v>
       </c>
@@ -15862,7 +15861,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="97" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>201927</v>
       </c>
@@ -15983,7 +15982,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="98" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>201931</v>
       </c>
@@ -16104,7 +16103,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="99" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>201933</v>
       </c>
@@ -16225,7 +16224,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="100" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>201936</v>
       </c>
@@ -16346,7 +16345,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="101" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>201940</v>
       </c>
@@ -16467,7 +16466,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="102" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>201954</v>
       </c>
@@ -16588,7 +16587,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="103" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>201967</v>
       </c>
@@ -16709,7 +16708,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="104" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>201972</v>
       </c>
@@ -16830,7 +16829,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="105" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>201973</v>
       </c>
@@ -16951,7 +16950,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="106" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>201974</v>
       </c>
@@ -17072,7 +17071,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="107" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>201975</v>
       </c>
@@ -17193,7 +17192,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="108" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>201981</v>
       </c>
@@ -17314,7 +17313,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="109" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>201987</v>
       </c>
@@ -17435,7 +17434,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="110" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>201994</v>
       </c>
@@ -17556,7 +17555,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="111" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>202216</v>
       </c>
@@ -17677,7 +17676,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="112" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>202224</v>
       </c>
@@ -17799,7 +17798,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="113" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>202232</v>
       </c>
@@ -17921,7 +17920,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="114" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>202245</v>
       </c>
@@ -18042,7 +18041,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="115" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>202249</v>
       </c>
@@ -18163,7 +18162,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="116" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>202256</v>
       </c>
@@ -18284,7 +18283,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="117" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>202266</v>
       </c>
@@ -18405,7 +18404,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="118" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>202290</v>
       </c>
@@ -18526,7 +18525,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="119" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>202294</v>
       </c>
@@ -18644,11 +18643,11 @@
         <v>0.42065313039451241</v>
       </c>
       <c r="AG119" s="2" t="str">
-        <f t="shared" ref="AG119" si="43">IF(AF119&gt;0.7,"High",IF(AF119&gt;0.3,"Moderate",IF(AF119&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="AG66:AG129" si="43">IF(AF119&gt;0.7,"High",IF(AF119&gt;0.3,"Moderate",IF(AF119&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
     </row>
-    <row r="120" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>203014</v>
       </c>
@@ -18769,7 +18768,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="121" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>203025</v>
       </c>
@@ -18890,7 +18889,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="122" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>203029</v>
       </c>
@@ -19011,7 +19010,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="123" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>203041</v>
       </c>
@@ -19132,7 +19131,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="124" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>203051</v>
       </c>
@@ -19253,7 +19252,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="125" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>203094</v>
       </c>
@@ -19374,7 +19373,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="126" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>204643</v>
       </c>
@@ -19495,7 +19494,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="127" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>204649</v>
       </c>
@@ -19616,7 +19615,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="128" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>204661</v>
       </c>
@@ -19737,7 +19736,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="129" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>204665</v>
       </c>
@@ -19858,7 +19857,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="130" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>204667</v>
       </c>
@@ -19979,7 +19978,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="131" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>204670</v>
       </c>
@@ -20100,7 +20099,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="132" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>204677</v>
       </c>
@@ -20221,7 +20220,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="133" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>204680</v>
       </c>
@@ -20342,7 +20341,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="134" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>205133</v>
       </c>
@@ -20463,7 +20462,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="135" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>205143</v>
       </c>
@@ -20581,11 +20580,11 @@
         <v>0.3095770233380376</v>
       </c>
       <c r="AG135" s="2" t="str">
-        <f t="shared" ref="AG135:AG142" si="64">IF(AF135&gt;0.7,"High",IF(AF135&gt;0.3,"Moderate",IF(AF135&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="AG130:AG193" si="64">IF(AF135&gt;0.7,"High",IF(AF135&gt;0.3,"Moderate",IF(AF135&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
     </row>
-    <row r="136" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>205158</v>
       </c>
@@ -20706,7 +20705,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="137" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>205165</v>
       </c>
@@ -20827,7 +20826,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="138" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>205173</v>
       </c>
@@ -20948,7 +20947,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="139" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>207507</v>
       </c>
@@ -21069,7 +21068,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="140" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>207510</v>
       </c>
@@ -21190,7 +21189,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="141" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>207521</v>
       </c>
@@ -21311,7 +21310,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="142" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>207536</v>
       </c>
@@ -21433,7 +21432,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="143" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>207547</v>
       </c>
@@ -21554,7 +21553,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="144" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>207580</v>
       </c>
@@ -21675,7 +21674,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="145" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>207583</v>
       </c>
@@ -21796,7 +21795,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="146" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>207585</v>
       </c>
@@ -21917,7 +21916,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="147" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>207587</v>
       </c>
@@ -22038,7 +22037,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="148" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>208407</v>
       </c>
@@ -22159,7 +22158,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="149" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>208421</v>
       </c>
@@ -22280,7 +22279,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="150" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>208425</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="151" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>208429</v>
       </c>
@@ -22522,7 +22521,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="152" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>208436</v>
       </c>
@@ -22643,7 +22642,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="153" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>208447</v>
       </c>
@@ -22764,7 +22763,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="154" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>208458</v>
       </c>
@@ -22885,7 +22884,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="155" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>208475</v>
       </c>
@@ -23006,7 +23005,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="156" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>208478</v>
       </c>
@@ -23127,7 +23126,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="157" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>208487</v>
       </c>
@@ -23248,7 +23247,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="158" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>302602</v>
       </c>
@@ -23369,7 +23368,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="159" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>302604</v>
       </c>
@@ -23490,7 +23489,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="160" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>302605</v>
       </c>
@@ -23611,7 +23610,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="161" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>302606</v>
       </c>
@@ -23732,7 +23731,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="162" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>302608</v>
       </c>
@@ -23853,7 +23852,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="163" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>302609</v>
       </c>
@@ -23974,7 +23973,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="164" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>302610</v>
       </c>
@@ -24095,7 +24094,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="165" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>302611</v>
       </c>
@@ -24216,7 +24215,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="166" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>302612</v>
       </c>
@@ -24337,7 +24336,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="167" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>302614</v>
       </c>
@@ -24458,7 +24457,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="168" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>302616</v>
       </c>
@@ -24579,7 +24578,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="169" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>302618</v>
       </c>
@@ -24700,7 +24699,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="170" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>302624</v>
       </c>
@@ -24821,7 +24820,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="171" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>302626</v>
       </c>
@@ -24942,7 +24941,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="172" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>302628</v>
       </c>
@@ -25063,7 +25062,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="173" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>302629</v>
       </c>
@@ -25184,7 +25183,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="174" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>302630</v>
       </c>
@@ -25305,7 +25304,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="175" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>302632</v>
       </c>
@@ -25426,7 +25425,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="176" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>302633</v>
       </c>
@@ -25547,7 +25546,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="177" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>302634</v>
       </c>
@@ -25668,7 +25667,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="178" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>302636</v>
       </c>
@@ -25789,7 +25788,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="179" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>302637</v>
       </c>
@@ -25910,7 +25909,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="180" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>302638</v>
       </c>
@@ -26031,7 +26030,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="181" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>302640</v>
       </c>
@@ -26152,7 +26151,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="182" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>302642</v>
       </c>
@@ -26273,7 +26272,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="183" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>302648</v>
       </c>
@@ -26394,7 +26393,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="184" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>302650</v>
       </c>
@@ -26515,7 +26514,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="185" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>302654</v>
       </c>
@@ -26636,7 +26635,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="186" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>302662</v>
       </c>
@@ -26757,7 +26756,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="187" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>302663</v>
       </c>
@@ -26878,7 +26877,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="188" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>302664</v>
       </c>
@@ -26999,7 +26998,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="189" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>302665</v>
       </c>
@@ -27120,7 +27119,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="190" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>302666</v>
       </c>
@@ -27241,7 +27240,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="191" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>302667</v>
       </c>
@@ -27362,7 +27361,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="192" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>302668</v>
       </c>
@@ -27483,7 +27482,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="193" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>302672</v>
       </c>
@@ -27604,7 +27603,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="194" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>302674</v>
       </c>
@@ -27725,7 +27724,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="195" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>302675</v>
       </c>
@@ -27846,7 +27845,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="196" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>302676</v>
       </c>
@@ -27967,7 +27966,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="197" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>302680</v>
       </c>
@@ -28088,7 +28087,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="198" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>302688</v>
       </c>
@@ -28209,7 +28208,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="199" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>302690</v>
       </c>
@@ -28330,7 +28329,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="200" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>302692</v>
       </c>
@@ -28451,7 +28450,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="201" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>302693</v>
       </c>
@@ -28572,7 +28571,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="202" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>302695</v>
       </c>
@@ -28693,7 +28692,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="203" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>302696</v>
       </c>
@@ -28814,7 +28813,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="204" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>302903</v>
       </c>
@@ -28935,7 +28934,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="205" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>302910</v>
       </c>
@@ -29056,7 +29055,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="206" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>302918</v>
       </c>
@@ -29177,7 +29176,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="207" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>302921</v>
       </c>
@@ -29298,7 +29297,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="208" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>302947</v>
       </c>
@@ -29419,7 +29418,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="209" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>302956</v>
       </c>
@@ -29540,7 +29539,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="210" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>302962</v>
       </c>
@@ -29661,7 +29660,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="211" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>302984</v>
       </c>
@@ -29782,7 +29781,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="212" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>302990</v>
       </c>
@@ -29903,7 +29902,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="213" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>303330</v>
       </c>
@@ -30024,7 +30023,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="214" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>303332</v>
       </c>
@@ -30145,7 +30144,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="215" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>303334</v>
       </c>
@@ -30266,7 +30265,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="216" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>303336</v>
       </c>
@@ -30387,7 +30386,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="217" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>303386</v>
       </c>
@@ -30508,7 +30507,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="218" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>303532</v>
       </c>
@@ -30629,7 +30628,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="219" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>303543</v>
       </c>
@@ -30750,7 +30749,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="220" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>303551</v>
       </c>
@@ -30871,7 +30870,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="221" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>303558</v>
       </c>
@@ -30992,7 +30991,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="222" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>303591</v>
       </c>
@@ -31113,7 +31112,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="223" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>304802</v>
       </c>
@@ -31234,7 +31233,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="224" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>304806</v>
       </c>
@@ -31355,7 +31354,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="225" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>304811</v>
       </c>
@@ -31476,7 +31475,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="226" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>304827</v>
       </c>
@@ -31597,7 +31596,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="227" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>304833</v>
       </c>
@@ -31718,7 +31717,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="228" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>304842</v>
       </c>
@@ -31839,7 +31838,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="229" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>304845</v>
       </c>
@@ -31960,7 +31959,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="230" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>304849</v>
       </c>
@@ -32081,7 +32080,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="231" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>304854</v>
       </c>
@@ -32202,7 +32201,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="232" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>304859</v>
       </c>
@@ -32323,7 +32322,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="233" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>304876</v>
       </c>
@@ -32444,7 +32443,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="234" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>304879</v>
       </c>
@@ -32565,7 +32564,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="235" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>304892</v>
       </c>
@@ -32686,7 +32685,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="236" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>305440</v>
       </c>
@@ -32807,7 +32806,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="237" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>305454</v>
       </c>
@@ -32928,7 +32927,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="238" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>305480</v>
       </c>
@@ -33049,7 +33048,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="239" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>305487</v>
       </c>
@@ -33170,7 +33169,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="240" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>305610</v>
       </c>
@@ -33291,7 +33290,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="241" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>305622</v>
       </c>
@@ -33412,7 +33411,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="242" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>305628</v>
       </c>
@@ -33533,7 +33532,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="243" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>305646</v>
       </c>
@@ -33654,7 +33653,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="244" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>305670</v>
       </c>
@@ -33775,7 +33774,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="245" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>305678</v>
       </c>
@@ -33896,7 +33895,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="246" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>305682</v>
       </c>
@@ -34017,7 +34016,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="247" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>305924</v>
       </c>
@@ -34138,7 +34137,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="248" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>305944</v>
       </c>
@@ -34259,7 +34258,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="249" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>305956</v>
       </c>
@@ -34380,7 +34379,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="250" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>305974</v>
       </c>
@@ -34501,7 +34500,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="251" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>305984</v>
       </c>
@@ -34622,7 +34621,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="252" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>305994</v>
       </c>
@@ -34743,7 +34742,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="253" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>306702</v>
       </c>
@@ -34864,7 +34863,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="254" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>306704</v>
       </c>
@@ -34985,7 +34984,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="255" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>306706</v>
       </c>
@@ -35106,7 +35105,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="256" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>306758</v>
       </c>
@@ -35227,7 +35226,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="257" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>306768</v>
       </c>
@@ -35348,7 +35347,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="258" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>306807</v>
       </c>
@@ -35469,7 +35468,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="259" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>306852</v>
       </c>
@@ -35590,7 +35589,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="260" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>306860</v>
       </c>
@@ -35711,7 +35710,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="261" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>306863</v>
       </c>
@@ -35832,7 +35831,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="262" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>306864</v>
       </c>
@@ -35953,7 +35952,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="263" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
         <v>306876</v>
       </c>
@@ -36074,7 +36073,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="264" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>308207</v>
       </c>
@@ -36195,7 +36194,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="265" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
         <v>308229</v>
       </c>
@@ -36316,7 +36315,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="266" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>308247</v>
       </c>
@@ -36437,7 +36436,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="267" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>308273</v>
       </c>
@@ -36558,7 +36557,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="268" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>308276</v>
       </c>
@@ -36679,7 +36678,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="269" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>308614</v>
       </c>
@@ -36800,7 +36799,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="270" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>308625</v>
       </c>
@@ -36921,7 +36920,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="271" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>308636</v>
       </c>
@@ -37042,7 +37041,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="272" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>308665</v>
       </c>
@@ -37163,7 +37162,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="273" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>308669</v>
       </c>
@@ -37284,7 +37283,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="274" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>308694</v>
       </c>
@@ -37405,7 +37404,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="275" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>309309</v>
       </c>
@@ -37526,7 +37525,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="276" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>309319</v>
       </c>
@@ -37647,7 +37646,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="277" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>309323</v>
       </c>
@@ -37768,7 +37767,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="278" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>309325</v>
       </c>
@@ -37889,7 +37888,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="279" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>309328</v>
       </c>
@@ -38010,7 +38009,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="280" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>309338</v>
       </c>
@@ -38131,7 +38130,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="281" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>309347</v>
       </c>
@@ -38252,7 +38251,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="282" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>309357</v>
       </c>
@@ -38373,7 +38372,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="283" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>309366</v>
       </c>
@@ -38494,7 +38493,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="284" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>309376</v>
       </c>
@@ -38615,7 +38614,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="285" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>309385</v>
       </c>
@@ -38736,7 +38735,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="286" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>309395</v>
       </c>
@@ -38857,7 +38856,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="287" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>400108</v>
       </c>
@@ -38940,7 +38939,7 @@
         <v>0.32625857530155145</v>
       </c>
       <c r="X287" s="2" t="str">
-        <f t="shared" ref="X287:X321" si="105">IF(W287&gt;0.7,"High",IF(W287&gt;0.3,"Moderate",IF(W287&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="X258:X321" si="105">IF(W287&gt;0.7,"High",IF(W287&gt;0.3,"Moderate",IF(W287&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
       <c r="Y287" s="2">
@@ -38976,11 +38975,11 @@
         <v>0.39933541904739905</v>
       </c>
       <c r="AG287" s="2" t="str">
-        <f t="shared" ref="AG287:AG321" si="106">IF(AF287&gt;0.7,"High",IF(AF287&gt;0.3,"Moderate",IF(AF287&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="AG258:AG321" si="106">IF(AF287&gt;0.7,"High",IF(AF287&gt;0.3,"Moderate",IF(AF287&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
     </row>
-    <row r="288" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>400114</v>
       </c>
@@ -39101,7 +39100,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="289" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>400134</v>
       </c>
@@ -39223,7 +39222,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="290" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>400138</v>
       </c>
@@ -39345,7 +39344,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="291" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>400156</v>
       </c>
@@ -39466,7 +39465,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="292" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>400158</v>
       </c>
@@ -39589,7 +39588,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="293" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>400160</v>
       </c>
@@ -39712,7 +39711,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="294" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>400173</v>
       </c>
@@ -39835,7 +39834,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="295" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>400177</v>
       </c>
@@ -39958,7 +39957,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="296" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>401807</v>
       </c>
@@ -40080,7 +40079,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="297" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>401823</v>
       </c>
@@ -40202,7 +40201,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="298" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>401831</v>
       </c>
@@ -40323,7 +40322,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="299" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>401855</v>
       </c>
@@ -40444,7 +40443,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="300" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>404104</v>
       </c>
@@ -40566,7 +40565,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="301" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>404109</v>
       </c>
@@ -40688,7 +40687,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="302" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>404111</v>
       </c>
@@ -40809,7 +40808,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="303" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>404123</v>
       </c>
@@ -40931,7 +40930,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="304" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>404138</v>
       </c>
@@ -41053,7 +41052,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="305" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>404147</v>
       </c>
@@ -41175,7 +41174,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="306" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>404161</v>
       </c>
@@ -41297,7 +41296,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="307" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>404190</v>
       </c>
@@ -41419,7 +41418,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="308" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>404414</v>
       </c>
@@ -41540,7 +41539,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="309" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>404419</v>
       </c>
@@ -41661,7 +41660,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="310" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>404433</v>
       </c>
@@ -41782,7 +41781,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="311" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>404442</v>
       </c>
@@ -41903,7 +41902,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="312" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>404471</v>
       </c>
@@ -42024,7 +42023,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="313" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>404480</v>
       </c>
@@ -42145,7 +42144,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="314" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>404712</v>
       </c>
@@ -42268,7 +42267,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="315" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>404717</v>
       </c>
@@ -42391,7 +42390,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="316" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>404730</v>
       </c>
@@ -42513,7 +42512,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="317" spans="1:38" s="11" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:38" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A317" s="11">
         <v>404733</v>
       </c>
@@ -42636,7 +42635,7 @@
       </c>
       <c r="AL317" s="2"/>
     </row>
-    <row r="318" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>404740</v>
       </c>
@@ -42757,7 +42756,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="319" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>404748</v>
       </c>
@@ -42878,7 +42877,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="320" spans="1:38" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>404753</v>
       </c>
@@ -43001,7 +43000,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="321" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>404764</v>
       </c>
@@ -43124,7 +43123,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="322" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>404769</v>
       </c>
@@ -43207,7 +43206,7 @@
         <v>0.34849192385127031</v>
       </c>
       <c r="X322" s="2" t="str">
-        <f t="shared" ref="X322:X347" si="119">IF(W322&gt;0.7,"High",IF(W322&gt;0.3,"Moderate",IF(W322&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="X322:X385" si="119">IF(W322&gt;0.7,"High",IF(W322&gt;0.3,"Moderate",IF(W322&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
       <c r="Y322" s="2">
@@ -43246,7 +43245,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="323" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>404775</v>
       </c>
@@ -43364,11 +43363,11 @@
         <v>0.31096368564930815</v>
       </c>
       <c r="AG323" s="2" t="str">
-        <f t="shared" ref="AG323:AG347" si="128">IF(AF323&gt;0.7,"High",IF(AF323&gt;0.3,"Moderate",IF(AF323&gt;0.15,"Low","No Impact")))</f>
+        <f t="shared" ref="AG322:AG385" si="128">IF(AF323&gt;0.7,"High",IF(AF323&gt;0.3,"Moderate",IF(AF323&gt;0.15,"Low","No Impact")))</f>
         <v>Moderate</v>
       </c>
     </row>
-    <row r="324" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>404794</v>
       </c>
@@ -43489,7 +43488,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="325" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>405015</v>
       </c>
@@ -43610,7 +43609,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="326" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>405039</v>
       </c>
@@ -43731,7 +43730,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="327" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>405063</v>
       </c>
@@ -43852,7 +43851,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="328" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>405071</v>
       </c>
@@ -43973,7 +43972,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="329" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>405079</v>
       </c>
@@ -44094,7 +44093,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="330" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>405094</v>
       </c>
@@ -44215,7 +44214,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="331" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>405557</v>
       </c>
@@ -44336,7 +44335,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="332" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>405566</v>
       </c>
@@ -44457,7 +44456,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="333" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>405585</v>
       </c>
@@ -44578,7 +44577,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="334" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>405595</v>
       </c>
@@ -44699,7 +44698,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="335" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>405747</v>
       </c>
@@ -44820,7 +44819,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="336" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>405760</v>
       </c>
@@ -44942,7 +44941,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="337" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>405787</v>
       </c>
@@ -45063,7 +45062,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="338" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>406528</v>
       </c>
@@ -45185,7 +45184,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="339" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A339" s="2">
         <v>406552</v>
       </c>
@@ -45306,7 +45305,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="340" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A340" s="2">
         <v>406576</v>
       </c>
@@ -45428,7 +45427,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="341" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A341" s="2">
         <v>408704</v>
       </c>
@@ -45550,7 +45549,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="342" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A342" s="2">
         <v>408725</v>
       </c>
@@ -45671,7 +45670,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="343" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A343" s="2">
         <v>408743</v>
       </c>
@@ -45794,7 +45793,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="344" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A344" s="2">
         <v>408747</v>
       </c>
@@ -45917,7 +45916,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="345" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>408782</v>
       </c>
@@ -46039,7 +46038,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="346" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>408786</v>
       </c>
@@ -46162,7 +46161,7 @@
         <v>High</v>
       </c>
     </row>
-    <row r="347" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>408790</v>
       </c>
@@ -46285,7 +46284,7 @@
         <v>Moderate</v>
       </c>
     </row>
-    <row r="348" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>453907</v>
       </c>
@@ -46406,7 +46405,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="349" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>453915</v>
       </c>
@@ -46527,7 +46526,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="350" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>453929</v>
       </c>
@@ -46648,7 +46647,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="351" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>453936</v>
       </c>
@@ -46769,7 +46768,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="352" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>453958</v>
       </c>
@@ -46890,7 +46889,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="353" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>453961</v>
       </c>
@@ -47011,7 +47010,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="354" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>453985</v>
       </c>
@@ -47132,7 +47131,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="355" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>456113</v>
       </c>
@@ -47253,7 +47252,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="356" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>456116</v>
       </c>
@@ -47374,7 +47373,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="357" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>456120</v>
       </c>
@@ -47495,7 +47494,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="358" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>456122</v>
       </c>
@@ -47616,7 +47615,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="359" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>456123</v>
       </c>
@@ -47737,7 +47736,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="360" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>456124</v>
       </c>
@@ -47858,7 +47857,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="361" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>456131</v>
       </c>
@@ -47979,7 +47978,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="362" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>456152</v>
       </c>
@@ -48100,7 +48099,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="363" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>456165</v>
       </c>
@@ -48221,7 +48220,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="364" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>456172</v>
       </c>
@@ -48342,7 +48341,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="365" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>456181</v>
       </c>
@@ -48463,7 +48462,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="366" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>456194</v>
       </c>
@@ -48584,7 +48583,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="367" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>457204</v>
       </c>
@@ -48705,7 +48704,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="368" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>457209</v>
       </c>
@@ -48826,7 +48825,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="369" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>457218</v>
       </c>
@@ -48947,7 +48946,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="370" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>457238</v>
       </c>
@@ -49068,7 +49067,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="371" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>457240</v>
       </c>
@@ -49189,7 +49188,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="372" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>457247</v>
       </c>
@@ -49310,7 +49309,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="373" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>457256</v>
       </c>
@@ -49431,7 +49430,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="374" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>457263</v>
       </c>
@@ -49552,7 +49551,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="375" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>457274</v>
       </c>
@@ -49673,7 +49672,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="376" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>457283</v>
       </c>
@@ -49794,7 +49793,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="377" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>458937</v>
       </c>
@@ -49915,7 +49914,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="378" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>458967</v>
       </c>
@@ -50036,7 +50035,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="379" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>458970</v>
       </c>
@@ -50157,7 +50156,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="380" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>458988</v>
       </c>
@@ -50278,7 +50277,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="381" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>458990</v>
       </c>
@@ -50399,7 +50398,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="382" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>501006</v>
       </c>
@@ -50520,7 +50519,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="383" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>501020</v>
       </c>
@@ -50641,7 +50640,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="384" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>501027</v>
       </c>
@@ -50762,7 +50761,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="385" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A385" s="2">
         <v>501033</v>
       </c>
@@ -50883,7 +50882,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="386" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A386" s="2">
         <v>501040</v>
       </c>
@@ -51004,7 +51003,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="387" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A387" s="2">
         <v>501054</v>
       </c>
@@ -51125,7 +51124,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="388" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A388" s="2">
         <v>501067</v>
       </c>
@@ -51246,7 +51245,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="389" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A389" s="2">
         <v>501081</v>
       </c>
@@ -51367,7 +51366,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="390" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
         <v>501085</v>
       </c>
@@ -51488,7 +51487,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="391" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
         <v>501088</v>
       </c>
@@ -51609,7 +51608,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="392" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
         <v>501094</v>
       </c>
@@ -51730,7 +51729,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="393" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>501095</v>
       </c>
@@ -51851,7 +51850,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="394" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>503813</v>
       </c>
@@ -51972,7 +51971,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="395" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>503847</v>
       </c>
@@ -52093,7 +52092,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="396" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>503858</v>
       </c>
@@ -52214,7 +52213,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="397" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>503861</v>
       </c>
@@ -52335,7 +52334,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="398" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>503874</v>
       </c>
@@ -52456,7 +52455,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="399" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>506403</v>
       </c>
@@ -52577,7 +52576,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="400" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A400" s="2">
         <v>506406</v>
       </c>
@@ -52698,7 +52697,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="401" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A401" s="2">
         <v>506428</v>
       </c>
@@ -52819,7 +52818,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="402" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A402" s="2">
         <v>506447</v>
       </c>
@@ -52940,7 +52939,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="403" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A403" s="2">
         <v>506450</v>
       </c>
@@ -53061,7 +53060,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="404" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A404" s="2">
         <v>506460</v>
       </c>
@@ -53182,7 +53181,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="405" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A405" s="2">
         <v>506469</v>
       </c>
@@ -53303,7 +53302,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="406" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A406" s="2">
         <v>506475</v>
       </c>
@@ -53424,7 +53423,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="407" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A407" s="2">
         <v>506479</v>
       </c>
@@ -53545,7 +53544,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="408" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A408" s="2">
         <v>506485</v>
       </c>
@@ -53666,7 +53665,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="409" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A409" s="2">
         <v>506486</v>
       </c>
@@ -53787,7 +53786,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="410" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A410" s="2">
         <v>506909</v>
       </c>
@@ -53908,7 +53907,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="411" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A411" s="2">
         <v>506915</v>
       </c>
@@ -54029,7 +54028,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="412" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A412" s="2">
         <v>506941</v>
       </c>
@@ -54150,7 +54149,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="413" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A413" s="2">
         <v>506944</v>
       </c>
@@ -54271,7 +54270,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="414" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A414" s="2">
         <v>506963</v>
       </c>
@@ -54392,7 +54391,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="415" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A415" s="2">
         <v>506991</v>
       </c>
@@ -54513,7 +54512,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="416" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A416" s="2">
         <v>507018</v>
       </c>
@@ -54634,7 +54633,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="417" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A417" s="2">
         <v>507037</v>
       </c>
@@ -54755,7 +54754,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="418" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A418" s="2">
         <v>507056</v>
       </c>
@@ -54876,7 +54875,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="419" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A419" s="2">
         <v>507066</v>
       </c>
@@ -54997,7 +54996,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="420" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A420" s="2">
         <v>507088</v>
       </c>
@@ -55118,7 +55117,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="421" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A421" s="2">
         <v>507605</v>
       </c>
@@ -55239,7 +55238,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="422" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A422" s="2">
         <v>507616</v>
       </c>
@@ -55360,7 +55359,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="423" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A423" s="2">
         <v>507619</v>
       </c>
@@ -55481,7 +55480,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="424" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A424" s="2">
         <v>507622</v>
       </c>
@@ -55602,7 +55601,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="425" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A425" s="2">
         <v>507633</v>
       </c>
@@ -55723,7 +55722,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="426" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A426" s="2">
         <v>507639</v>
       </c>
@@ -55844,7 +55843,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="427" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A427" s="2">
         <v>507655</v>
       </c>
@@ -55965,7 +55964,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="428" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A428" s="2">
         <v>507672</v>
       </c>
@@ -56086,7 +56085,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="429" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A429" s="2">
         <v>507683</v>
       </c>
@@ -56207,7 +56206,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="430" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A430" s="2">
         <v>508110</v>
       </c>
@@ -56328,7 +56327,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="431" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A431" s="2">
         <v>508112</v>
       </c>
@@ -56449,7 +56448,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="432" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A432" s="2">
         <v>508122</v>
       </c>
@@ -56570,7 +56569,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="433" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A433" s="2">
         <v>508125</v>
       </c>
@@ -56691,7 +56690,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="434" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A434" s="2">
         <v>508131</v>
       </c>
@@ -56812,7 +56811,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="435" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A435" s="2">
         <v>508134</v>
       </c>
@@ -56933,7 +56932,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="436" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A436" s="2">
         <v>508140</v>
       </c>
@@ -57054,7 +57053,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="437" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A437" s="2">
         <v>508153</v>
       </c>
@@ -57175,7 +57174,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="438" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A438" s="2">
         <v>508172</v>
       </c>
@@ -57296,7 +57295,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="439" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A439" s="2">
         <v>508182</v>
       </c>
@@ -57417,7 +57416,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="440" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A440" s="2">
         <v>508185</v>
       </c>
@@ -57538,7 +57537,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="441" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A441" s="2">
         <v>508190</v>
       </c>
@@ -57659,7 +57658,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="442" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A442" s="2">
         <v>508194</v>
       </c>
@@ -57780,7 +57779,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="443" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A443" s="2">
         <v>508811</v>
       </c>
@@ -57901,7 +57900,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="444" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A444" s="2">
         <v>508827</v>
       </c>
@@ -58022,7 +58021,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="445" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A445" s="2">
         <v>508844</v>
       </c>
@@ -58143,7 +58142,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="446" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A446" s="2">
         <v>508850</v>
       </c>
@@ -58264,7 +58263,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="447" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A447" s="2">
         <v>508861</v>
       </c>
@@ -58385,7 +58384,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="448" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A448" s="2">
         <v>508867</v>
       </c>
@@ -58506,7 +58505,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="449" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A449" s="2">
         <v>508878</v>
       </c>
@@ -58627,7 +58626,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="450" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A450" s="2">
         <v>508889</v>
       </c>
@@ -58748,7 +58747,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="451" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A451" s="2">
         <v>508894</v>
       </c>
@@ -58869,7 +58868,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="452" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A452" s="2">
         <v>552710</v>
       </c>
@@ -58990,7 +58989,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="453" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A453" s="2">
         <v>552712</v>
       </c>
@@ -59111,7 +59110,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="454" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A454" s="2">
         <v>552717</v>
       </c>
@@ -59232,7 +59231,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="455" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A455" s="2">
         <v>552721</v>
       </c>
@@ -59353,7 +59352,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="456" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A456" s="2">
         <v>552730</v>
       </c>
@@ -59474,7 +59473,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="457" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A457" s="2">
         <v>552738</v>
       </c>
@@ -59595,7 +59594,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="458" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A458" s="2">
         <v>552743</v>
       </c>
@@ -59716,7 +59715,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="459" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A459" s="2">
         <v>552747</v>
       </c>
@@ -59837,7 +59836,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="460" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A460" s="2">
         <v>552756</v>
       </c>
@@ -59958,7 +59957,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="461" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A461" s="2">
         <v>552760</v>
       </c>
@@ -60079,7 +60078,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="462" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A462" s="2">
         <v>552764</v>
       </c>
@@ -60200,7 +60199,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="463" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A463" s="2">
         <v>552769</v>
       </c>
@@ -60321,7 +60320,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="464" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A464" s="2">
         <v>552777</v>
       </c>
@@ -60442,7 +60441,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="465" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A465" s="2">
         <v>553221</v>
       </c>
@@ -60563,7 +60562,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="466" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A466" s="2">
         <v>553224</v>
       </c>
@@ -60684,7 +60683,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="467" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A467" s="2">
         <v>553230</v>
       </c>
@@ -60805,7 +60804,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="468" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A468" s="2">
         <v>553267</v>
       </c>
@@ -60926,7 +60925,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="469" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A469" s="2">
         <v>553282</v>
       </c>
@@ -61047,7 +61046,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="470" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A470" s="2">
         <v>553288</v>
       </c>
@@ -61168,7 +61167,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="471" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A471" s="2">
         <v>553291</v>
       </c>
@@ -61289,7 +61288,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="472" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A472" s="2">
         <v>554906</v>
       </c>
@@ -61410,7 +61409,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="473" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A473" s="2">
         <v>554908</v>
       </c>
@@ -61531,7 +61530,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="474" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A474" s="2">
         <v>554909</v>
       </c>
@@ -61652,7 +61651,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="475" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A475" s="2">
         <v>554918</v>
       </c>
@@ -61773,7 +61772,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="476" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A476" s="2">
         <v>554952</v>
       </c>
@@ -61894,7 +61893,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="477" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A477" s="2">
         <v>554961</v>
       </c>
@@ -62015,7 +62014,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="478" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A478" s="2">
         <v>554977</v>
       </c>
@@ -62136,7 +62135,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="479" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A479" s="2">
         <v>554979</v>
       </c>
@@ -62257,7 +62256,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="480" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A480" s="2">
         <v>554994</v>
       </c>
@@ -62378,7 +62377,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="481" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A481" s="2">
         <v>555202</v>
       </c>
@@ -62499,7 +62498,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="482" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A482" s="2">
         <v>555233</v>
       </c>
@@ -62620,7 +62619,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="483" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A483" s="2">
         <v>555239</v>
       </c>
@@ -62741,7 +62740,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="484" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A484" s="2">
         <v>555255</v>
       </c>
@@ -62862,7 +62861,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="485" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A485" s="2">
         <v>555270</v>
       </c>
@@ -62983,7 +62982,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="486" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A486" s="2">
         <v>557312</v>
       </c>
@@ -63104,7 +63103,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="487" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A487" s="2">
         <v>557315</v>
       </c>
@@ -63225,7 +63224,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="488" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A488" s="2">
         <v>557336</v>
       </c>
@@ -63346,7 +63345,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="489" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A489" s="2">
         <v>557345</v>
       </c>
@@ -63467,7 +63466,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="490" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A490" s="2">
         <v>557364</v>
       </c>
@@ -63588,7 +63587,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="491" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A491" s="2">
         <v>557385</v>
       </c>
@@ -63709,7 +63708,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="492" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A492" s="2">
         <v>557704</v>
       </c>
@@ -63830,7 +63829,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="493" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A493" s="2">
         <v>557725</v>
       </c>
@@ -63951,7 +63950,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="494" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A494" s="2">
         <v>557734</v>
       </c>
@@ -64072,7 +64071,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="495" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A495" s="2">
         <v>557773</v>
       </c>
@@ -64193,7 +64192,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="496" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A496" s="2">
         <v>557790</v>
       </c>
@@ -64314,7 +64313,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="497" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A497" s="2">
         <v>558503</v>
       </c>
@@ -64435,7 +64434,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="498" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A498" s="2">
         <v>558527</v>
       </c>
@@ -64556,7 +64555,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="499" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A499" s="2">
         <v>558542</v>
       </c>
@@ -64677,7 +64676,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="500" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A500" s="2">
         <v>558549</v>
       </c>
@@ -64798,7 +64797,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="501" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A501" s="2">
         <v>558558</v>
       </c>
@@ -64919,7 +64918,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="502" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A502" s="2">
         <v>558573</v>
       </c>
@@ -65040,7 +65039,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="503" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A503" s="2">
         <v>558576</v>
       </c>
@@ -65161,7 +65160,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="504" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A504" s="2">
         <v>558592</v>
       </c>
@@ -65282,7 +65281,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="505" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A505" s="2">
         <v>559408</v>
       </c>
@@ -65403,7 +65402,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="506" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A506" s="2">
         <v>559451</v>
       </c>
@@ -65524,7 +65523,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="507" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A507" s="2">
         <v>559482</v>
       </c>
@@ -65645,7 +65644,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="508" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A508" s="2">
         <v>559486</v>
       </c>
@@ -65766,7 +65765,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="509" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A509" s="2">
         <v>559494</v>
       </c>
@@ -65887,7 +65886,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="510" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A510" s="2">
         <v>603602</v>
       </c>
@@ -66008,7 +66007,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="511" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A511" s="2">
         <v>603605</v>
       </c>
@@ -66129,7 +66128,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="512" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A512" s="2">
         <v>603611</v>
       </c>
@@ -66250,7 +66249,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="513" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A513" s="2">
         <v>603626</v>
       </c>
@@ -66371,7 +66370,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="514" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A514" s="2">
         <v>603644</v>
       </c>
@@ -66492,7 +66491,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="515" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A515" s="2">
         <v>603668</v>
       </c>
@@ -66613,7 +66612,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="516" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A516" s="2">
         <v>603671</v>
       </c>
@@ -66734,7 +66733,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="517" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A517" s="2">
         <v>603677</v>
       </c>
@@ -66855,7 +66854,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="518" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A518" s="2">
         <v>605814</v>
       </c>
@@ -66976,7 +66975,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="519" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A519" s="2">
         <v>605835</v>
       </c>
@@ -67097,7 +67096,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="520" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A520" s="2">
         <v>605856</v>
       </c>
@@ -67218,7 +67217,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="521" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A521" s="2">
         <v>605865</v>
       </c>
@@ -67339,7 +67338,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="522" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A522" s="2">
         <v>605874</v>
       </c>
@@ -67460,7 +67459,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="523" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A523" s="2">
         <v>605880</v>
       </c>
@@ -67581,7 +67580,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="524" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A524" s="2">
         <v>605883</v>
       </c>
@@ -67702,7 +67701,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="525" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A525" s="2">
         <v>609018</v>
       </c>
@@ -67823,7 +67822,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="526" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A526" s="2">
         <v>609023</v>
       </c>
@@ -67944,7 +67943,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="527" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A527" s="2">
         <v>609027</v>
       </c>
@@ -68065,7 +68064,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="528" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A528" s="2">
         <v>609029</v>
       </c>
@@ -68186,7 +68185,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="529" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A529" s="2">
         <v>609032</v>
       </c>
@@ -68307,7 +68306,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="530" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A530" s="2">
         <v>609033</v>
       </c>
@@ -68428,7 +68427,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="531" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A531" s="2">
         <v>609047</v>
       </c>
@@ -68549,7 +68548,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="532" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A532" s="2">
         <v>609050</v>
       </c>
@@ -68670,7 +68669,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="533" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A533" s="2">
         <v>609086</v>
       </c>
@@ -68791,7 +68790,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="534" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A534" s="2">
         <v>609089</v>
       </c>
@@ -68912,7 +68911,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="535" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A535" s="2">
         <v>609092</v>
       </c>
@@ -69033,7 +69032,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="536" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A536" s="2">
         <v>609108</v>
       </c>
@@ -69154,7 +69153,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="537" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A537" s="2">
         <v>609117</v>
       </c>
@@ -69275,7 +69274,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="538" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A538" s="2">
         <v>609120</v>
       </c>
@@ -69396,7 +69395,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="539" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A539" s="2">
         <v>609127</v>
       </c>
@@ -69517,7 +69516,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="540" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A540" s="2">
         <v>609131</v>
       </c>
@@ -69638,7 +69637,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="541" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A541" s="2">
         <v>609135</v>
       </c>
@@ -69759,7 +69758,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="542" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A542" s="2">
         <v>609138</v>
       </c>
@@ -69880,7 +69879,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="543" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A543" s="2">
         <v>609141</v>
       </c>
@@ -70001,7 +70000,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="544" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A544" s="2">
         <v>609153</v>
       </c>
@@ -70122,7 +70121,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="545" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A545" s="2">
         <v>609159</v>
       </c>
@@ -70243,7 +70242,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="546" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A546" s="2">
         <v>609162</v>
       </c>
@@ -70364,7 +70363,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="547" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A547" s="2">
         <v>609194</v>
       </c>
@@ -70486,13 +70485,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK547" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Chittagong"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
